--- a/output/yearly_population_iteration_27_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_27_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4416</v>
+        <v>7182</v>
       </c>
       <c r="C2" t="n">
-        <v>10752</v>
+        <v>5320</v>
       </c>
       <c r="D2" t="n">
-        <v>23525</v>
+        <v>30587</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3393</v>
+        <v>4069</v>
       </c>
       <c r="C3" t="n">
-        <v>7021</v>
+        <v>4243</v>
       </c>
       <c r="D3" t="n">
-        <v>15487</v>
+        <v>20618</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2799</v>
+        <v>3239</v>
       </c>
       <c r="C4" t="n">
-        <v>5045</v>
+        <v>4388</v>
       </c>
       <c r="D4" t="n">
-        <v>8255</v>
+        <v>9074</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1733</v>
+        <v>2121</v>
       </c>
       <c r="C5" t="n">
-        <v>4409</v>
+        <v>3934</v>
       </c>
       <c r="D5" t="n">
-        <v>3212</v>
+        <v>3294</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>926</v>
+        <v>1188</v>
       </c>
       <c r="C6" t="n">
-        <v>3238</v>
+        <v>2509</v>
       </c>
       <c r="D6" t="n">
-        <v>1266</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>415</v>
+        <v>562</v>
       </c>
       <c r="C7" t="n">
-        <v>2030</v>
+        <v>1355</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>155</v>
+        <v>206</v>
       </c>
       <c r="C8" t="n">
-        <v>946</v>
+        <v>641</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>392</v>
+        <v>323</v>
       </c>
       <c r="D9" t="n">
         <v>306</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1052,7 +1052,7 @@
         <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4831</v>
+        <v>9086</v>
       </c>
       <c r="C2" t="n">
-        <v>11530</v>
+        <v>8969</v>
       </c>
       <c r="D2" t="n">
-        <v>22675</v>
+        <v>38454</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3154</v>
+        <v>4423</v>
       </c>
       <c r="C3" t="n">
-        <v>7652</v>
+        <v>4164</v>
       </c>
       <c r="D3" t="n">
-        <v>15539</v>
+        <v>20588</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2639</v>
+        <v>3111</v>
       </c>
       <c r="C4" t="n">
-        <v>5869</v>
+        <v>4227</v>
       </c>
       <c r="D4" t="n">
-        <v>9184</v>
+        <v>10682</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1922</v>
+        <v>2299</v>
       </c>
       <c r="C5" t="n">
-        <v>4561</v>
+        <v>4023</v>
       </c>
       <c r="D5" t="n">
-        <v>3858</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1147</v>
+        <v>1444</v>
       </c>
       <c r="C6" t="n">
-        <v>3692</v>
+        <v>3127</v>
       </c>
       <c r="D6" t="n">
-        <v>1547</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>561</v>
+        <v>749</v>
       </c>
       <c r="C7" t="n">
-        <v>2561</v>
+        <v>1850</v>
       </c>
       <c r="D7" t="n">
-        <v>738</v>
+        <v>750</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>232</v>
+        <v>310</v>
       </c>
       <c r="C8" t="n">
-        <v>1393</v>
+        <v>948</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="C9" t="n">
-        <v>619</v>
+        <v>450</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1363,7 +1363,7 @@
         <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6391</v>
+        <v>9738</v>
       </c>
       <c r="C2" t="n">
-        <v>8897</v>
+        <v>5265</v>
       </c>
       <c r="D2" t="n">
-        <v>23179</v>
+        <v>30536</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3122</v>
+        <v>5098</v>
       </c>
       <c r="C3" t="n">
-        <v>8191</v>
+        <v>5459</v>
       </c>
       <c r="D3" t="n">
-        <v>15400</v>
+        <v>21721</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2433</v>
+        <v>3101</v>
       </c>
       <c r="C4" t="n">
-        <v>6517</v>
+        <v>4111</v>
       </c>
       <c r="D4" t="n">
-        <v>9731</v>
+        <v>11681</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1963</v>
+        <v>2340</v>
       </c>
       <c r="C5" t="n">
-        <v>4962</v>
+        <v>3986</v>
       </c>
       <c r="D5" t="n">
-        <v>4507</v>
+        <v>4843</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1321</v>
+        <v>1645</v>
       </c>
       <c r="C6" t="n">
-        <v>3973</v>
+        <v>3468</v>
       </c>
       <c r="D6" t="n">
-        <v>1822</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>712</v>
+        <v>917</v>
       </c>
       <c r="C7" t="n">
-        <v>3014</v>
+        <v>2344</v>
       </c>
       <c r="D7" t="n">
-        <v>841</v>
+        <v>846</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>313</v>
+        <v>423</v>
       </c>
       <c r="C8" t="n">
-        <v>1825</v>
+        <v>1291</v>
       </c>
       <c r="D8" t="n">
-        <v>487</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="C9" t="n">
-        <v>900</v>
+        <v>640</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>404</v>
+        <v>323</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1674,7 +1674,7 @@
         <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5811</v>
+        <v>8888</v>
       </c>
       <c r="C2" t="n">
-        <v>6121</v>
+        <v>3580</v>
       </c>
       <c r="D2" t="n">
-        <v>19282</v>
+        <v>25262</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4041</v>
+        <v>5899</v>
       </c>
       <c r="C3" t="n">
-        <v>11550</v>
+        <v>7529</v>
       </c>
       <c r="D3" t="n">
-        <v>17034</v>
+        <v>23606</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1813</v>
+        <v>2162</v>
       </c>
       <c r="C4" t="n">
-        <v>8329</v>
+        <v>6115</v>
       </c>
       <c r="D4" t="n">
-        <v>9467</v>
+        <v>10972</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1220</v>
+        <v>1519</v>
       </c>
       <c r="C5" t="n">
-        <v>3893</v>
+        <v>3398</v>
       </c>
       <c r="D5" t="n">
-        <v>2997</v>
+        <v>3166</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>657</v>
+        <v>847</v>
       </c>
       <c r="C6" t="n">
-        <v>2953</v>
+        <v>2297</v>
       </c>
       <c r="D6" t="n">
-        <v>824</v>
+        <v>829</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="C7" t="n">
-        <v>1788</v>
+        <v>1265</v>
       </c>
       <c r="D7" t="n">
-        <v>477</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="C8" t="n">
-        <v>882</v>
+        <v>627</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>395</v>
+        <v>316</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D10" t="n">
         <v>201</v>
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1971,7 +1971,7 @@
         <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3562</v>
+        <v>5381</v>
       </c>
       <c r="C2" t="n">
-        <v>3595</v>
+        <v>2348</v>
       </c>
       <c r="D2" t="n">
-        <v>13589</v>
+        <v>17251</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4131</v>
+        <v>6232</v>
       </c>
       <c r="C3" t="n">
-        <v>8263</v>
+        <v>5175</v>
       </c>
       <c r="D3" t="n">
-        <v>16522</v>
+        <v>22471</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2329</v>
+        <v>3090</v>
       </c>
       <c r="C4" t="n">
-        <v>9959</v>
+        <v>6887</v>
       </c>
       <c r="D4" t="n">
-        <v>10359</v>
+        <v>12789</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1366</v>
+        <v>1667</v>
       </c>
       <c r="C5" t="n">
-        <v>5787</v>
+        <v>4612</v>
       </c>
       <c r="D5" t="n">
-        <v>3770</v>
+        <v>4104</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>785</v>
+        <v>1018</v>
       </c>
       <c r="C6" t="n">
-        <v>3420</v>
+        <v>2795</v>
       </c>
       <c r="D6" t="n">
-        <v>1046</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>270</v>
+        <v>366</v>
       </c>
       <c r="C7" t="n">
-        <v>2253</v>
+        <v>1659</v>
       </c>
       <c r="D7" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>1149</v>
+        <v>822</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>441</v>
+        <v>367</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2167,7 +2167,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2268,7 +2268,7 @@
         <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3235</v>
+        <v>5631</v>
       </c>
       <c r="C2" t="n">
-        <v>12944</v>
+        <v>4596</v>
       </c>
       <c r="D2" t="n">
-        <v>12064</v>
+        <v>25661</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3273</v>
+        <v>4930</v>
       </c>
       <c r="C3" t="n">
-        <v>5433</v>
+        <v>3361</v>
       </c>
       <c r="D3" t="n">
-        <v>15012</v>
+        <v>20389</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2673</v>
+        <v>3835</v>
       </c>
       <c r="C4" t="n">
-        <v>8937</v>
+        <v>5955</v>
       </c>
       <c r="D4" t="n">
-        <v>11049</v>
+        <v>13980</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1574</v>
+        <v>2012</v>
       </c>
       <c r="C5" t="n">
-        <v>7589</v>
+        <v>5586</v>
       </c>
       <c r="D5" t="n">
-        <v>4667</v>
+        <v>5273</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>934</v>
+        <v>1184</v>
       </c>
       <c r="C6" t="n">
-        <v>4465</v>
+        <v>3587</v>
       </c>
       <c r="D6" t="n">
-        <v>1424</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>411</v>
+        <v>550</v>
       </c>
       <c r="C7" t="n">
-        <v>2743</v>
+        <v>2175</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c r="C8" t="n">
-        <v>1603</v>
+        <v>1174</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>713</v>
+        <v>547</v>
       </c>
       <c r="D9" t="n">
         <v>264</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2461,7 +2461,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
         <v>186</v>
@@ -2495,7 +2495,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2523,7 +2523,7 @@
         <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1949</v>
+        <v>3364</v>
       </c>
       <c r="C2" t="n">
-        <v>6153</v>
+        <v>2137</v>
       </c>
       <c r="D2" t="n">
-        <v>8454</v>
+        <v>17681</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3150</v>
+        <v>4918</v>
       </c>
       <c r="C3" t="n">
-        <v>7740</v>
+        <v>3678</v>
       </c>
       <c r="D3" t="n">
-        <v>14369</v>
+        <v>20490</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2945</v>
+        <v>4227</v>
       </c>
       <c r="C4" t="n">
-        <v>8498</v>
+        <v>5531</v>
       </c>
       <c r="D4" t="n">
-        <v>11630</v>
+        <v>14891</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1640</v>
+        <v>2099</v>
       </c>
       <c r="C5" t="n">
-        <v>8985</v>
+        <v>6531</v>
       </c>
       <c r="D5" t="n">
-        <v>4907</v>
+        <v>5712</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>750</v>
+        <v>989</v>
       </c>
       <c r="C6" t="n">
-        <v>5364</v>
+        <v>4343</v>
       </c>
       <c r="D6" t="n">
-        <v>1387</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="C7" t="n">
-        <v>2885</v>
+        <v>2231</v>
       </c>
       <c r="D7" t="n">
-        <v>588</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>1185</v>
+        <v>904</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -2758,7 +2758,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
         <v>182</v>
@@ -2792,7 +2792,7 @@
         <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2820,7 +2820,7 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2178</v>
+        <v>4116</v>
       </c>
       <c r="C2" t="n">
-        <v>4799</v>
+        <v>4692</v>
       </c>
       <c r="D2" t="n">
-        <v>16089</v>
+        <v>22262</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2260</v>
+        <v>3617</v>
       </c>
       <c r="C3" t="n">
-        <v>6275</v>
+        <v>2637</v>
       </c>
       <c r="D3" t="n">
-        <v>12736</v>
+        <v>18731</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2677</v>
+        <v>3980</v>
       </c>
       <c r="C4" t="n">
-        <v>7971</v>
+        <v>4579</v>
       </c>
       <c r="D4" t="n">
-        <v>11697</v>
+        <v>15352</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1923</v>
+        <v>2615</v>
       </c>
       <c r="C5" t="n">
-        <v>8669</v>
+        <v>6006</v>
       </c>
       <c r="D5" t="n">
-        <v>5725</v>
+        <v>7003</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>982</v>
+        <v>1287</v>
       </c>
       <c r="C6" t="n">
-        <v>6863</v>
+        <v>5269</v>
       </c>
       <c r="D6" t="n">
-        <v>1842</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>271</v>
+        <v>369</v>
       </c>
       <c r="C7" t="n">
-        <v>3912</v>
+        <v>3122</v>
       </c>
       <c r="D7" t="n">
-        <v>689</v>
+        <v>713</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1807</v>
+        <v>1402</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>581</v>
+        <v>480</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1585</v>
+        <v>3035</v>
       </c>
       <c r="C2" t="n">
-        <v>3527</v>
+        <v>2610</v>
       </c>
       <c r="D2" t="n">
-        <v>11893</v>
+        <v>16146</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1959</v>
+        <v>3311</v>
       </c>
       <c r="C3" t="n">
-        <v>5243</v>
+        <v>3132</v>
       </c>
       <c r="D3" t="n">
-        <v>12567</v>
+        <v>18135</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2337</v>
+        <v>3566</v>
       </c>
       <c r="C4" t="n">
-        <v>7290</v>
+        <v>3813</v>
       </c>
       <c r="D4" t="n">
-        <v>11583</v>
+        <v>15486</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2065</v>
+        <v>2882</v>
       </c>
       <c r="C5" t="n">
-        <v>8573</v>
+        <v>5591</v>
       </c>
       <c r="D5" t="n">
-        <v>6236</v>
+        <v>7886</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1143</v>
+        <v>1515</v>
       </c>
       <c r="C6" t="n">
-        <v>7691</v>
+        <v>5717</v>
       </c>
       <c r="D6" t="n">
-        <v>2209</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>243</v>
+        <v>347</v>
       </c>
       <c r="C7" t="n">
-        <v>4872</v>
+        <v>3830</v>
       </c>
       <c r="D7" t="n">
-        <v>770</v>
+        <v>818</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>2303</v>
+        <v>1844</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>660</v>
+        <v>563</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
         <v>178</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2285</v>
+        <v>5113</v>
       </c>
       <c r="C2" t="n">
-        <v>7171</v>
+        <v>8321</v>
       </c>
       <c r="D2" t="n">
-        <v>13670</v>
+        <v>29844</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1541</v>
+        <v>2699</v>
       </c>
       <c r="C3" t="n">
-        <v>4082</v>
+        <v>2593</v>
       </c>
       <c r="D3" t="n">
-        <v>11802</v>
+        <v>16735</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1918</v>
+        <v>3048</v>
       </c>
       <c r="C4" t="n">
-        <v>6293</v>
+        <v>3439</v>
       </c>
       <c r="D4" t="n">
-        <v>11251</v>
+        <v>15396</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1992</v>
+        <v>2843</v>
       </c>
       <c r="C5" t="n">
-        <v>7889</v>
+        <v>4740</v>
       </c>
       <c r="D5" t="n">
-        <v>6765</v>
+        <v>8591</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1343</v>
+        <v>1846</v>
       </c>
       <c r="C6" t="n">
-        <v>7958</v>
+        <v>5618</v>
       </c>
       <c r="D6" t="n">
-        <v>2683</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>455</v>
+        <v>643</v>
       </c>
       <c r="C7" t="n">
-        <v>5892</v>
+        <v>4549</v>
       </c>
       <c r="D7" t="n">
-        <v>931</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>3205</v>
+        <v>2581</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>1181</v>
+        <v>995</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
         <v>95</v>
@@ -3739,7 +3739,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4369</v>
+        <v>7433</v>
       </c>
       <c r="C2" t="n">
-        <v>7777</v>
+        <v>5459</v>
       </c>
       <c r="D2" t="n">
-        <v>13787</v>
+        <v>13435</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1653</v>
+        <v>3659</v>
       </c>
       <c r="C2" t="n">
-        <v>4187</v>
+        <v>4727</v>
       </c>
       <c r="D2" t="n">
-        <v>10170</v>
+        <v>21965</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2133</v>
+        <v>3710</v>
       </c>
       <c r="C3" t="n">
-        <v>5114</v>
+        <v>4145</v>
       </c>
       <c r="D3" t="n">
-        <v>12851</v>
+        <v>19010</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2800</v>
+        <v>4184</v>
       </c>
       <c r="C4" t="n">
-        <v>8968</v>
+        <v>5031</v>
       </c>
       <c r="D4" t="n">
-        <v>11668</v>
+        <v>15724</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1277</v>
+        <v>1784</v>
       </c>
       <c r="C5" t="n">
-        <v>11315</v>
+        <v>7443</v>
       </c>
       <c r="D5" t="n">
-        <v>6211</v>
+        <v>7816</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>420</v>
+        <v>594</v>
       </c>
       <c r="C6" t="n">
-        <v>7255</v>
+        <v>5614</v>
       </c>
       <c r="D6" t="n">
-        <v>2082</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="C7" t="n">
-        <v>3140</v>
+        <v>2529</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1157</v>
+        <v>975</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
         <v>93</v>
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6475</v>
+        <v>7229</v>
       </c>
       <c r="C2" t="n">
-        <v>7999</v>
+        <v>3469</v>
       </c>
       <c r="D2" t="n">
-        <v>23364</v>
+        <v>20387</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1858</v>
+        <v>3157</v>
       </c>
       <c r="C3" t="n">
-        <v>3919</v>
+        <v>2751</v>
       </c>
       <c r="D3" t="n">
-        <v>2955</v>
+        <v>2896</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4308</v>
+        <v>5398</v>
       </c>
       <c r="C2" t="n">
-        <v>5367</v>
+        <v>4206</v>
       </c>
       <c r="D2" t="n">
-        <v>18269</v>
+        <v>27094</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3417</v>
+        <v>4267</v>
       </c>
       <c r="C3" t="n">
-        <v>5370</v>
+        <v>2722</v>
       </c>
       <c r="D3" t="n">
-        <v>6166</v>
+        <v>5621</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>841</v>
+        <v>1406</v>
       </c>
       <c r="C4" t="n">
-        <v>2341</v>
+        <v>1657</v>
       </c>
       <c r="D4" t="n">
-        <v>1776</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5228</v>
+        <v>5681</v>
       </c>
       <c r="C2" t="n">
-        <v>8466</v>
+        <v>8552</v>
       </c>
       <c r="D2" t="n">
-        <v>33467</v>
+        <v>26587</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3173</v>
+        <v>3970</v>
       </c>
       <c r="C3" t="n">
-        <v>4646</v>
+        <v>3056</v>
       </c>
       <c r="D3" t="n">
-        <v>7658</v>
+        <v>8651</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1806</v>
+        <v>2416</v>
       </c>
       <c r="C4" t="n">
-        <v>4007</v>
+        <v>2225</v>
       </c>
       <c r="D4" t="n">
-        <v>2564</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>399</v>
+        <v>625</v>
       </c>
       <c r="C5" t="n">
-        <v>1377</v>
+        <v>1001</v>
       </c>
       <c r="D5" t="n">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5207,7 +5207,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>76</v>
@@ -5336,7 +5336,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>7350</v>
       </c>
       <c r="C2" t="n">
-        <v>6440</v>
+        <v>5512</v>
       </c>
       <c r="D2" t="n">
-        <v>26304</v>
+        <v>34885</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3383</v>
+        <v>3928</v>
       </c>
       <c r="C3" t="n">
-        <v>5755</v>
+        <v>5122</v>
       </c>
       <c r="D3" t="n">
-        <v>11041</v>
+        <v>10768</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2089</v>
+        <v>2721</v>
       </c>
       <c r="C4" t="n">
-        <v>4267</v>
+        <v>2625</v>
       </c>
       <c r="D4" t="n">
-        <v>3415</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>902</v>
+        <v>1249</v>
       </c>
       <c r="C5" t="n">
-        <v>2711</v>
+        <v>1605</v>
       </c>
       <c r="D5" t="n">
-        <v>1430</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>237</v>
+        <v>333</v>
       </c>
       <c r="C6" t="n">
-        <v>833</v>
+        <v>653</v>
       </c>
       <c r="D6" t="n">
         <v>955</v>
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
         <v>660</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
         <v>478</v>
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7282</v>
+        <v>7042</v>
       </c>
       <c r="C2" t="n">
-        <v>7614</v>
+        <v>8050</v>
       </c>
       <c r="D2" t="n">
-        <v>33965</v>
+        <v>35081</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3091</v>
+        <v>4053</v>
       </c>
       <c r="C3" t="n">
-        <v>4999</v>
+        <v>4359</v>
       </c>
       <c r="D3" t="n">
-        <v>11839</v>
+        <v>12865</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1697</v>
+        <v>2050</v>
       </c>
       <c r="C4" t="n">
-        <v>4118</v>
+        <v>3278</v>
       </c>
       <c r="D4" t="n">
-        <v>4104</v>
+        <v>4123</v>
       </c>
     </row>
     <row r="5">
@@ -5798,10 +5798,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>771</v>
+        <v>1043</v>
       </c>
       <c r="C5" t="n">
-        <v>2567</v>
+        <v>1547</v>
       </c>
       <c r="D5" t="n">
         <v>1389</v>
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>267</v>
+        <v>371</v>
       </c>
       <c r="C6" t="n">
-        <v>1180</v>
+        <v>763</v>
       </c>
       <c r="D6" t="n">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>375</v>
+        <v>317</v>
       </c>
       <c r="D7" t="n">
         <v>514</v>
@@ -5840,10 +5840,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
         <v>360</v>
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5156</v>
+        <v>6490</v>
       </c>
       <c r="C2" t="n">
-        <v>6633</v>
+        <v>4469</v>
       </c>
       <c r="D2" t="n">
-        <v>26108</v>
+        <v>40906</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4293</v>
+        <v>4608</v>
       </c>
       <c r="C3" t="n">
-        <v>5613</v>
+        <v>5605</v>
       </c>
       <c r="D3" t="n">
-        <v>14684</v>
+        <v>15650</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2092</v>
+        <v>2686</v>
       </c>
       <c r="C4" t="n">
-        <v>4565</v>
+        <v>3863</v>
       </c>
       <c r="D4" t="n">
-        <v>5499</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1086</v>
+        <v>1382</v>
       </c>
       <c r="C5" t="n">
-        <v>3421</v>
+        <v>2528</v>
       </c>
       <c r="D5" t="n">
-        <v>1894</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>479</v>
+        <v>650</v>
       </c>
       <c r="C6" t="n">
-        <v>1951</v>
+        <v>1190</v>
       </c>
       <c r="D6" t="n">
-        <v>892</v>
+        <v>889</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>215</v>
       </c>
       <c r="C7" t="n">
-        <v>824</v>
+        <v>570</v>
       </c>
       <c r="D7" t="n">
         <v>554</v>
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>303</v>
+        <v>274</v>
       </c>
       <c r="D8" t="n">
         <v>385</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6213,7 +6213,7 @@
         <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4375</v>
+        <v>5387</v>
       </c>
       <c r="C2" t="n">
-        <v>10676</v>
+        <v>5411</v>
       </c>
       <c r="D2" t="n">
-        <v>23070</v>
+        <v>41698</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3881</v>
+        <v>4546</v>
       </c>
       <c r="C3" t="n">
-        <v>5340</v>
+        <v>4315</v>
       </c>
       <c r="D3" t="n">
-        <v>15454</v>
+        <v>18564</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2700</v>
+        <v>3136</v>
       </c>
       <c r="C4" t="n">
-        <v>5053</v>
+        <v>4769</v>
       </c>
       <c r="D4" t="n">
-        <v>7095</v>
+        <v>7452</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1389</v>
+        <v>1765</v>
       </c>
       <c r="C5" t="n">
-        <v>3932</v>
+        <v>3205</v>
       </c>
       <c r="D5" t="n">
-        <v>2493</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>699</v>
+        <v>923</v>
       </c>
       <c r="C6" t="n">
-        <v>2704</v>
+        <v>1882</v>
       </c>
       <c r="D6" t="n">
-        <v>1044</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="7">
@@ -6448,10 +6448,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>377</v>
       </c>
       <c r="C7" t="n">
-        <v>1409</v>
+        <v>886</v>
       </c>
       <c r="D7" t="n">
         <v>607</v>
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>563</v>
+        <v>424</v>
       </c>
       <c r="D8" t="n">
         <v>405</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6552,7 +6552,7 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>28</v>
@@ -6650,7 +6650,7 @@
         <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_27_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_27_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7182</v>
+        <v>5205</v>
       </c>
       <c r="C2" t="n">
-        <v>5320</v>
+        <v>3721</v>
       </c>
       <c r="D2" t="n">
-        <v>30587</v>
+        <v>24368</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4069</v>
+        <v>2965</v>
       </c>
       <c r="C3" t="n">
-        <v>4243</v>
+        <v>5604</v>
       </c>
       <c r="D3" t="n">
-        <v>20618</v>
+        <v>12135</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3239</v>
+        <v>2521</v>
       </c>
       <c r="C4" t="n">
-        <v>4388</v>
+        <v>5825</v>
       </c>
       <c r="D4" t="n">
-        <v>9074</v>
+        <v>6613</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2121</v>
+        <v>1700</v>
       </c>
       <c r="C5" t="n">
-        <v>3934</v>
+        <v>4275</v>
       </c>
       <c r="D5" t="n">
-        <v>3294</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1188</v>
+        <v>1001</v>
       </c>
       <c r="C6" t="n">
-        <v>2509</v>
+        <v>3154</v>
       </c>
       <c r="D6" t="n">
-        <v>1273</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>562</v>
+        <v>465</v>
       </c>
       <c r="C7" t="n">
-        <v>1355</v>
+        <v>1980</v>
       </c>
       <c r="D7" t="n">
-        <v>676</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="C8" t="n">
-        <v>641</v>
+        <v>932</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>323</v>
+        <v>390</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9086</v>
+        <v>6389</v>
       </c>
       <c r="C2" t="n">
-        <v>8969</v>
+        <v>6224</v>
       </c>
       <c r="D2" t="n">
-        <v>38454</v>
+        <v>32740</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4423</v>
+        <v>3214</v>
       </c>
       <c r="C3" t="n">
-        <v>4164</v>
+        <v>4178</v>
       </c>
       <c r="D3" t="n">
-        <v>20588</v>
+        <v>12983</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3111</v>
+        <v>2349</v>
       </c>
       <c r="C4" t="n">
-        <v>4227</v>
+        <v>5541</v>
       </c>
       <c r="D4" t="n">
-        <v>10682</v>
+        <v>7249</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2299</v>
+        <v>1817</v>
       </c>
       <c r="C5" t="n">
-        <v>4023</v>
+        <v>4915</v>
       </c>
       <c r="D5" t="n">
-        <v>4050</v>
+        <v>3216</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1444</v>
+        <v>1186</v>
       </c>
       <c r="C6" t="n">
-        <v>3127</v>
+        <v>3597</v>
       </c>
       <c r="D6" t="n">
-        <v>1566</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>749</v>
+        <v>622</v>
       </c>
       <c r="C7" t="n">
-        <v>1850</v>
+        <v>2508</v>
       </c>
       <c r="D7" t="n">
-        <v>750</v>
+        <v>708</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>310</v>
+        <v>265</v>
       </c>
       <c r="C8" t="n">
-        <v>948</v>
+        <v>1374</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>450</v>
+        <v>618</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9738</v>
+        <v>9149</v>
       </c>
       <c r="C2" t="n">
-        <v>5265</v>
+        <v>15775</v>
       </c>
       <c r="D2" t="n">
-        <v>30536</v>
+        <v>34108</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5098</v>
+        <v>3640</v>
       </c>
       <c r="C3" t="n">
-        <v>5459</v>
+        <v>4456</v>
       </c>
       <c r="D3" t="n">
-        <v>21721</v>
+        <v>14660</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3101</v>
+        <v>2301</v>
       </c>
       <c r="C4" t="n">
-        <v>4111</v>
+        <v>4823</v>
       </c>
       <c r="D4" t="n">
-        <v>11681</v>
+        <v>7909</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2340</v>
+        <v>1814</v>
       </c>
       <c r="C5" t="n">
-        <v>3986</v>
+        <v>5030</v>
       </c>
       <c r="D5" t="n">
-        <v>4843</v>
+        <v>3668</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1645</v>
+        <v>1316</v>
       </c>
       <c r="C6" t="n">
-        <v>3468</v>
+        <v>4073</v>
       </c>
       <c r="D6" t="n">
-        <v>1903</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>917</v>
+        <v>768</v>
       </c>
       <c r="C7" t="n">
-        <v>2344</v>
+        <v>2955</v>
       </c>
       <c r="D7" t="n">
-        <v>846</v>
+        <v>781</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>423</v>
+        <v>356</v>
       </c>
       <c r="C8" t="n">
-        <v>1291</v>
+        <v>1804</v>
       </c>
       <c r="D8" t="n">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="C9" t="n">
-        <v>640</v>
+        <v>900</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>323</v>
+        <v>409</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1531,7 +1531,7 @@
         <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
         <v>167</v>
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
         <v>103</v>
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8888</v>
+        <v>8102</v>
       </c>
       <c r="C2" t="n">
-        <v>3580</v>
+        <v>10727</v>
       </c>
       <c r="D2" t="n">
-        <v>25262</v>
+        <v>27849</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5899</v>
+        <v>4286</v>
       </c>
       <c r="C3" t="n">
-        <v>7529</v>
+        <v>8115</v>
       </c>
       <c r="D3" t="n">
-        <v>23606</v>
+        <v>15940</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2162</v>
+        <v>1676</v>
       </c>
       <c r="C4" t="n">
-        <v>6115</v>
+        <v>7514</v>
       </c>
       <c r="D4" t="n">
-        <v>10972</v>
+        <v>7698</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1519</v>
+        <v>1215</v>
       </c>
       <c r="C5" t="n">
-        <v>3398</v>
+        <v>3991</v>
       </c>
       <c r="D5" t="n">
-        <v>3166</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>847</v>
+        <v>709</v>
       </c>
       <c r="C6" t="n">
-        <v>2297</v>
+        <v>2895</v>
       </c>
       <c r="D6" t="n">
-        <v>829</v>
+        <v>765</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>390</v>
+        <v>328</v>
       </c>
       <c r="C7" t="n">
-        <v>1265</v>
+        <v>1767</v>
       </c>
       <c r="D7" t="n">
-        <v>485</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>627</v>
+        <v>882</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>316</v>
+        <v>400</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1828,7 +1828,7 @@
         <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
         <v>201</v>
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>163</v>
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>123</v>
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
         <v>77</v>
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5381</v>
+        <v>4746</v>
       </c>
       <c r="C2" t="n">
-        <v>2348</v>
+        <v>4457</v>
       </c>
       <c r="D2" t="n">
-        <v>17251</v>
+        <v>19623</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6232</v>
+        <v>5002</v>
       </c>
       <c r="C3" t="n">
-        <v>5175</v>
+        <v>8435</v>
       </c>
       <c r="D3" t="n">
-        <v>22471</v>
+        <v>16641</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3090</v>
+        <v>2312</v>
       </c>
       <c r="C4" t="n">
-        <v>6887</v>
+        <v>7928</v>
       </c>
       <c r="D4" t="n">
-        <v>12789</v>
+        <v>8877</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1667</v>
+        <v>1322</v>
       </c>
       <c r="C5" t="n">
-        <v>4612</v>
+        <v>5553</v>
       </c>
       <c r="D5" t="n">
-        <v>4104</v>
+        <v>3164</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1018</v>
+        <v>845</v>
       </c>
       <c r="C6" t="n">
-        <v>2795</v>
+        <v>3422</v>
       </c>
       <c r="D6" t="n">
-        <v>1067</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>366</v>
+        <v>309</v>
       </c>
       <c r="C7" t="n">
-        <v>1659</v>
+        <v>2231</v>
       </c>
       <c r="D7" t="n">
-        <v>531</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>822</v>
+        <v>1151</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>367</v>
+        <v>457</v>
       </c>
       <c r="D9" t="n">
         <v>258</v>
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
         <v>211</v>
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5631</v>
+        <v>4371</v>
       </c>
       <c r="C2" t="n">
-        <v>4596</v>
+        <v>7419</v>
       </c>
       <c r="D2" t="n">
-        <v>25661</v>
+        <v>22925</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4930</v>
+        <v>4104</v>
       </c>
       <c r="C3" t="n">
-        <v>3361</v>
+        <v>5821</v>
       </c>
       <c r="D3" t="n">
-        <v>20389</v>
+        <v>16085</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3835</v>
+        <v>2991</v>
       </c>
       <c r="C4" t="n">
-        <v>5955</v>
+        <v>8011</v>
       </c>
       <c r="D4" t="n">
-        <v>13980</v>
+        <v>9874</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2012</v>
+        <v>1550</v>
       </c>
       <c r="C5" t="n">
-        <v>5586</v>
+        <v>6554</v>
       </c>
       <c r="D5" t="n">
-        <v>5273</v>
+        <v>3945</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1184</v>
+        <v>962</v>
       </c>
       <c r="C6" t="n">
-        <v>3587</v>
+        <v>4383</v>
       </c>
       <c r="D6" t="n">
-        <v>1519</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>550</v>
+        <v>460</v>
       </c>
       <c r="C7" t="n">
-        <v>2175</v>
+        <v>2743</v>
       </c>
       <c r="D7" t="n">
-        <v>609</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="C8" t="n">
-        <v>1174</v>
+        <v>1617</v>
       </c>
       <c r="D8" t="n">
         <v>357</v>
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>547</v>
+        <v>719</v>
       </c>
       <c r="D9" t="n">
         <v>264</v>
@@ -2450,7 +2450,7 @@
         <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>273</v>
+        <v>313</v>
       </c>
       <c r="D10" t="n">
         <v>215</v>
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2537,7 +2537,7 @@
         <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3364</v>
+        <v>2589</v>
       </c>
       <c r="C2" t="n">
-        <v>2137</v>
+        <v>3455</v>
       </c>
       <c r="D2" t="n">
-        <v>17681</v>
+        <v>16026</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4918</v>
+        <v>4021</v>
       </c>
       <c r="C3" t="n">
-        <v>3678</v>
+        <v>6180</v>
       </c>
       <c r="D3" t="n">
-        <v>20490</v>
+        <v>16436</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4227</v>
+        <v>3324</v>
       </c>
       <c r="C4" t="n">
-        <v>5531</v>
+        <v>7898</v>
       </c>
       <c r="D4" t="n">
-        <v>14891</v>
+        <v>10622</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2099</v>
+        <v>1643</v>
       </c>
       <c r="C5" t="n">
-        <v>6531</v>
+        <v>7821</v>
       </c>
       <c r="D5" t="n">
-        <v>5712</v>
+        <v>4168</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>989</v>
+        <v>816</v>
       </c>
       <c r="C6" t="n">
-        <v>4343</v>
+        <v>5318</v>
       </c>
       <c r="D6" t="n">
-        <v>1468</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>2231</v>
+        <v>2921</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>904</v>
+        <v>1195</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2747,7 +2747,7 @@
         <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
         <v>288</v>
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2834,7 +2834,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4116</v>
+        <v>3345</v>
       </c>
       <c r="C2" t="n">
-        <v>4692</v>
+        <v>5001</v>
       </c>
       <c r="D2" t="n">
-        <v>22262</v>
+        <v>14661</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3617</v>
+        <v>2938</v>
       </c>
       <c r="C3" t="n">
-        <v>2637</v>
+        <v>4407</v>
       </c>
       <c r="D3" t="n">
-        <v>18731</v>
+        <v>15433</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3980</v>
+        <v>3148</v>
       </c>
       <c r="C4" t="n">
-        <v>4579</v>
+        <v>6925</v>
       </c>
       <c r="D4" t="n">
-        <v>15352</v>
+        <v>11192</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2615</v>
+        <v>2051</v>
       </c>
       <c r="C5" t="n">
-        <v>6006</v>
+        <v>7768</v>
       </c>
       <c r="D5" t="n">
-        <v>7003</v>
+        <v>4970</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1287</v>
+        <v>1036</v>
       </c>
       <c r="C6" t="n">
-        <v>5269</v>
+        <v>6378</v>
       </c>
       <c r="D6" t="n">
-        <v>2019</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>369</v>
+        <v>309</v>
       </c>
       <c r="C7" t="n">
-        <v>3122</v>
+        <v>3940</v>
       </c>
       <c r="D7" t="n">
-        <v>713</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>1402</v>
+        <v>1843</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>480</v>
+        <v>602</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
         <v>174</v>
@@ -3083,7 +3083,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>134</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3035</v>
+        <v>2217</v>
       </c>
       <c r="C2" t="n">
-        <v>2610</v>
+        <v>2596</v>
       </c>
       <c r="D2" t="n">
-        <v>16146</v>
+        <v>11937</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3311</v>
+        <v>2688</v>
       </c>
       <c r="C3" t="n">
-        <v>3132</v>
+        <v>4254</v>
       </c>
       <c r="D3" t="n">
-        <v>18135</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3566</v>
+        <v>2842</v>
       </c>
       <c r="C4" t="n">
-        <v>3813</v>
+        <v>5898</v>
       </c>
       <c r="D4" t="n">
-        <v>15486</v>
+        <v>11529</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2882</v>
+        <v>2238</v>
       </c>
       <c r="C5" t="n">
-        <v>5591</v>
+        <v>7597</v>
       </c>
       <c r="D5" t="n">
-        <v>7886</v>
+        <v>5631</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1515</v>
+        <v>1226</v>
       </c>
       <c r="C6" t="n">
-        <v>5717</v>
+        <v>7074</v>
       </c>
       <c r="D6" t="n">
-        <v>2464</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>347</v>
+        <v>279</v>
       </c>
       <c r="C7" t="n">
-        <v>3830</v>
+        <v>4806</v>
       </c>
       <c r="D7" t="n">
-        <v>818</v>
+        <v>744</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>1844</v>
+        <v>2363</v>
       </c>
       <c r="D8" t="n">
-        <v>417</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>563</v>
+        <v>699</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
         <v>178</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>137</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5113</v>
+        <v>3928</v>
       </c>
       <c r="C2" t="n">
-        <v>8321</v>
+        <v>12992</v>
       </c>
       <c r="D2" t="n">
-        <v>29844</v>
+        <v>16030</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2699</v>
+        <v>2121</v>
       </c>
       <c r="C3" t="n">
-        <v>2593</v>
+        <v>3221</v>
       </c>
       <c r="D3" t="n">
-        <v>16735</v>
+        <v>13264</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3048</v>
+        <v>2446</v>
       </c>
       <c r="C4" t="n">
-        <v>3439</v>
+        <v>5080</v>
       </c>
       <c r="D4" t="n">
-        <v>15396</v>
+        <v>11606</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2843</v>
+        <v>2225</v>
       </c>
       <c r="C5" t="n">
-        <v>4740</v>
+        <v>6753</v>
       </c>
       <c r="D5" t="n">
-        <v>8591</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1846</v>
+        <v>1456</v>
       </c>
       <c r="C6" t="n">
-        <v>5618</v>
+        <v>7215</v>
       </c>
       <c r="D6" t="n">
-        <v>3160</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>643</v>
+        <v>510</v>
       </c>
       <c r="C7" t="n">
-        <v>4549</v>
+        <v>5648</v>
       </c>
       <c r="D7" t="n">
-        <v>1019</v>
+        <v>866</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>2581</v>
+        <v>3247</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>995</v>
+        <v>1243</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>326</v>
+        <v>369</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
+        <v>92</v>
+      </c>
+      <c r="D12" t="n">
         <v>93</v>
-      </c>
-      <c r="D12" t="n">
-        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7433</v>
+        <v>5473</v>
       </c>
       <c r="C2" t="n">
-        <v>5459</v>
+        <v>8229</v>
       </c>
       <c r="D2" t="n">
-        <v>13435</v>
+        <v>6789</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3659</v>
+        <v>2807</v>
       </c>
       <c r="C2" t="n">
-        <v>4727</v>
+        <v>7484</v>
       </c>
       <c r="D2" t="n">
-        <v>21965</v>
+        <v>11798</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3710</v>
+        <v>2944</v>
       </c>
       <c r="C3" t="n">
-        <v>4145</v>
+        <v>5693</v>
       </c>
       <c r="D3" t="n">
-        <v>19010</v>
+        <v>14539</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4184</v>
+        <v>3286</v>
       </c>
       <c r="C4" t="n">
-        <v>5031</v>
+        <v>7325</v>
       </c>
       <c r="D4" t="n">
-        <v>15724</v>
+        <v>11862</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1784</v>
+        <v>1407</v>
       </c>
       <c r="C5" t="n">
-        <v>7443</v>
+        <v>10000</v>
       </c>
       <c r="D5" t="n">
-        <v>7816</v>
+        <v>5654</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>594</v>
+        <v>471</v>
       </c>
       <c r="C6" t="n">
-        <v>5614</v>
+        <v>6949</v>
       </c>
       <c r="D6" t="n">
-        <v>2417</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>2529</v>
+        <v>3182</v>
       </c>
       <c r="D7" t="n">
-        <v>579</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>975</v>
+        <v>1218</v>
       </c>
       <c r="D8" t="n">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>319</v>
+        <v>361</v>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>90</v>
+      </c>
+      <c r="D11" t="n">
         <v>91</v>
-      </c>
-      <c r="D11" t="n">
-        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7229</v>
+        <v>6392</v>
       </c>
       <c r="C2" t="n">
-        <v>3469</v>
+        <v>5077</v>
       </c>
       <c r="D2" t="n">
-        <v>20387</v>
+        <v>15117</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3157</v>
+        <v>2326</v>
       </c>
       <c r="C3" t="n">
-        <v>2751</v>
+        <v>4147</v>
       </c>
       <c r="D3" t="n">
-        <v>2896</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5398</v>
+        <v>4597</v>
       </c>
       <c r="C2" t="n">
-        <v>4206</v>
+        <v>7874</v>
       </c>
       <c r="D2" t="n">
-        <v>27094</v>
+        <v>28508</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4267</v>
+        <v>3578</v>
       </c>
       <c r="C3" t="n">
-        <v>2722</v>
+        <v>4030</v>
       </c>
       <c r="D3" t="n">
-        <v>5621</v>
+        <v>3888</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1406</v>
+        <v>1044</v>
       </c>
       <c r="C4" t="n">
-        <v>1657</v>
+        <v>2472</v>
       </c>
       <c r="D4" t="n">
-        <v>1765</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5681</v>
+        <v>5134</v>
       </c>
       <c r="C2" t="n">
-        <v>8552</v>
+        <v>7064</v>
       </c>
       <c r="D2" t="n">
-        <v>26587</v>
+        <v>21187</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3970</v>
+        <v>3356</v>
       </c>
       <c r="C3" t="n">
-        <v>3056</v>
+        <v>5302</v>
       </c>
       <c r="D3" t="n">
-        <v>8651</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2416</v>
+        <v>1965</v>
       </c>
       <c r="C4" t="n">
-        <v>2225</v>
+        <v>3303</v>
       </c>
       <c r="D4" t="n">
-        <v>2451</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>625</v>
+        <v>480</v>
       </c>
       <c r="C5" t="n">
-        <v>1001</v>
+        <v>1447</v>
       </c>
       <c r="D5" t="n">
-        <v>1253</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7350</v>
+        <v>5423</v>
       </c>
       <c r="C2" t="n">
-        <v>5512</v>
+        <v>6369</v>
       </c>
       <c r="D2" t="n">
-        <v>34885</v>
+        <v>20281</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3928</v>
+        <v>3445</v>
       </c>
       <c r="C3" t="n">
-        <v>5122</v>
+        <v>5404</v>
       </c>
       <c r="D3" t="n">
-        <v>10768</v>
+        <v>9088</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2721</v>
+        <v>2264</v>
       </c>
       <c r="C4" t="n">
-        <v>2625</v>
+        <v>4308</v>
       </c>
       <c r="D4" t="n">
-        <v>3507</v>
+        <v>2906</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1249</v>
+        <v>1001</v>
       </c>
       <c r="C5" t="n">
-        <v>1605</v>
+        <v>2365</v>
       </c>
       <c r="D5" t="n">
-        <v>1409</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>333</v>
+        <v>274</v>
       </c>
       <c r="C6" t="n">
-        <v>653</v>
+        <v>882</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7042</v>
+        <v>5497</v>
       </c>
       <c r="C2" t="n">
-        <v>8050</v>
+        <v>7355</v>
       </c>
       <c r="D2" t="n">
-        <v>35081</v>
+        <v>23242</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4053</v>
+        <v>3201</v>
       </c>
       <c r="C3" t="n">
-        <v>4359</v>
+        <v>4831</v>
       </c>
       <c r="D3" t="n">
-        <v>12865</v>
+        <v>9549</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2050</v>
+        <v>1760</v>
       </c>
       <c r="C4" t="n">
-        <v>3278</v>
+        <v>4023</v>
       </c>
       <c r="D4" t="n">
-        <v>4123</v>
+        <v>3443</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1043</v>
+        <v>855</v>
       </c>
       <c r="C5" t="n">
-        <v>1547</v>
+        <v>2447</v>
       </c>
       <c r="D5" t="n">
-        <v>1389</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>371</v>
+        <v>299</v>
       </c>
       <c r="C6" t="n">
-        <v>763</v>
+        <v>1098</v>
       </c>
       <c r="D6" t="n">
-        <v>785</v>
+        <v>764</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>317</v>
+        <v>389</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6490</v>
+        <v>4927</v>
       </c>
       <c r="C2" t="n">
-        <v>4469</v>
+        <v>10017</v>
       </c>
       <c r="D2" t="n">
-        <v>40906</v>
+        <v>20244</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4608</v>
+        <v>3612</v>
       </c>
       <c r="C3" t="n">
-        <v>5605</v>
+        <v>5422</v>
       </c>
       <c r="D3" t="n">
-        <v>15650</v>
+        <v>11146</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2686</v>
+        <v>2180</v>
       </c>
       <c r="C4" t="n">
-        <v>3863</v>
+        <v>4389</v>
       </c>
       <c r="D4" t="n">
-        <v>5720</v>
+        <v>4536</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1382</v>
+        <v>1159</v>
       </c>
       <c r="C5" t="n">
-        <v>2528</v>
+        <v>3334</v>
       </c>
       <c r="D5" t="n">
-        <v>1897</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>650</v>
+        <v>538</v>
       </c>
       <c r="C6" t="n">
-        <v>1190</v>
+        <v>1861</v>
       </c>
       <c r="D6" t="n">
-        <v>889</v>
+        <v>833</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="C7" t="n">
-        <v>570</v>
+        <v>791</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>274</v>
+        <v>314</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
         <v>120</v>
@@ -6238,7 +6238,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5387</v>
+        <v>3601</v>
       </c>
       <c r="C2" t="n">
-        <v>5411</v>
+        <v>6001</v>
       </c>
       <c r="D2" t="n">
-        <v>41698</v>
+        <v>19480</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4546</v>
+        <v>3500</v>
       </c>
       <c r="C3" t="n">
-        <v>4315</v>
+        <v>6862</v>
       </c>
       <c r="D3" t="n">
-        <v>18564</v>
+        <v>11799</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3136</v>
+        <v>2473</v>
       </c>
       <c r="C4" t="n">
-        <v>4769</v>
+        <v>4882</v>
       </c>
       <c r="D4" t="n">
-        <v>7452</v>
+        <v>5667</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1765</v>
+        <v>1469</v>
       </c>
       <c r="C5" t="n">
-        <v>3205</v>
+        <v>3809</v>
       </c>
       <c r="D5" t="n">
-        <v>2518</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>923</v>
+        <v>766</v>
       </c>
       <c r="C6" t="n">
-        <v>1882</v>
+        <v>2631</v>
       </c>
       <c r="D6" t="n">
-        <v>1060</v>
+        <v>967</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>317</v>
       </c>
       <c r="C7" t="n">
-        <v>886</v>
+        <v>1356</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>424</v>
+        <v>556</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6507,7 +6507,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -6524,7 +6524,7 @@
         <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6633,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_27_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_27_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5205</v>
+        <v>696</v>
       </c>
       <c r="C2" t="n">
-        <v>3721</v>
+        <v>4076</v>
       </c>
       <c r="D2" t="n">
-        <v>24368</v>
+        <v>11021</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2965</v>
+        <v>1152</v>
       </c>
       <c r="C3" t="n">
-        <v>5604</v>
+        <v>9955</v>
       </c>
       <c r="D3" t="n">
-        <v>12135</v>
+        <v>12705</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2521</v>
+        <v>798</v>
       </c>
       <c r="C4" t="n">
-        <v>5825</v>
+        <v>10542</v>
       </c>
       <c r="D4" t="n">
-        <v>6613</v>
+        <v>5996</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1700</v>
+        <v>420</v>
       </c>
       <c r="C5" t="n">
-        <v>4275</v>
+        <v>6155</v>
       </c>
       <c r="D5" t="n">
-        <v>2650</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1001</v>
+        <v>182</v>
       </c>
       <c r="C6" t="n">
-        <v>3154</v>
+        <v>2698</v>
       </c>
       <c r="D6" t="n">
-        <v>1128</v>
+        <v>740</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>465</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>1980</v>
+        <v>952</v>
       </c>
       <c r="D7" t="n">
-        <v>651</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>932</v>
+        <v>369</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>390</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6389</v>
+        <v>844</v>
       </c>
       <c r="C2" t="n">
-        <v>6224</v>
+        <v>4259</v>
       </c>
       <c r="D2" t="n">
-        <v>32740</v>
+        <v>11844</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3214</v>
+        <v>795</v>
       </c>
       <c r="C3" t="n">
-        <v>4178</v>
+        <v>6126</v>
       </c>
       <c r="D3" t="n">
-        <v>12983</v>
+        <v>11554</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2349</v>
+        <v>836</v>
       </c>
       <c r="C4" t="n">
-        <v>5541</v>
+        <v>10012</v>
       </c>
       <c r="D4" t="n">
-        <v>7249</v>
+        <v>7037</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1817</v>
+        <v>522</v>
       </c>
       <c r="C5" t="n">
-        <v>4915</v>
+        <v>8318</v>
       </c>
       <c r="D5" t="n">
-        <v>3216</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1186</v>
+        <v>260</v>
       </c>
       <c r="C6" t="n">
-        <v>3597</v>
+        <v>4355</v>
       </c>
       <c r="D6" t="n">
-        <v>1346</v>
+        <v>927</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>622</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>2508</v>
+        <v>1765</v>
       </c>
       <c r="D7" t="n">
-        <v>708</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>265</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1374</v>
+        <v>623</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>618</v>
+        <v>320</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>286</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9149</v>
+        <v>459</v>
       </c>
       <c r="C2" t="n">
-        <v>15775</v>
+        <v>1855</v>
       </c>
       <c r="D2" t="n">
-        <v>34108</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3640</v>
+        <v>778</v>
       </c>
       <c r="C3" t="n">
-        <v>4456</v>
+        <v>5213</v>
       </c>
       <c r="D3" t="n">
-        <v>14660</v>
+        <v>11293</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2301</v>
+        <v>909</v>
       </c>
       <c r="C4" t="n">
-        <v>4823</v>
+        <v>9347</v>
       </c>
       <c r="D4" t="n">
-        <v>7909</v>
+        <v>7637</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1814</v>
+        <v>527</v>
       </c>
       <c r="C5" t="n">
-        <v>5030</v>
+        <v>9850</v>
       </c>
       <c r="D5" t="n">
-        <v>3668</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1316</v>
+        <v>221</v>
       </c>
       <c r="C6" t="n">
-        <v>4073</v>
+        <v>5402</v>
       </c>
       <c r="D6" t="n">
-        <v>1597</v>
+        <v>939</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>768</v>
+        <v>68</v>
       </c>
       <c r="C7" t="n">
-        <v>2955</v>
+        <v>1631</v>
       </c>
       <c r="D7" t="n">
-        <v>781</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>356</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1804</v>
+        <v>521</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>900</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>409</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>219</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8102</v>
+        <v>418</v>
       </c>
       <c r="C2" t="n">
-        <v>10727</v>
+        <v>7655</v>
       </c>
       <c r="D2" t="n">
-        <v>27849</v>
+        <v>9115</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4286</v>
+        <v>546</v>
       </c>
       <c r="C3" t="n">
-        <v>8115</v>
+        <v>3153</v>
       </c>
       <c r="D3" t="n">
-        <v>15940</v>
+        <v>10056</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1676</v>
+        <v>758</v>
       </c>
       <c r="C4" t="n">
-        <v>7514</v>
+        <v>7138</v>
       </c>
       <c r="D4" t="n">
-        <v>7698</v>
+        <v>8109</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1215</v>
+        <v>615</v>
       </c>
       <c r="C5" t="n">
-        <v>3991</v>
+        <v>9498</v>
       </c>
       <c r="D5" t="n">
-        <v>2551</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>709</v>
+        <v>310</v>
       </c>
       <c r="C6" t="n">
-        <v>2895</v>
+        <v>7461</v>
       </c>
       <c r="D6" t="n">
-        <v>765</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>328</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>1767</v>
+        <v>3251</v>
       </c>
       <c r="D7" t="n">
-        <v>478</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>882</v>
+        <v>955</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>400</v>
+        <v>339</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
+        <v>69</v>
+      </c>
+      <c r="D14" t="n">
         <v>67</v>
-      </c>
-      <c r="D14" t="n">
-        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4746</v>
+        <v>279</v>
       </c>
       <c r="C2" t="n">
-        <v>4457</v>
+        <v>3594</v>
       </c>
       <c r="D2" t="n">
-        <v>19623</v>
+        <v>7334</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5002</v>
+        <v>438</v>
       </c>
       <c r="C3" t="n">
-        <v>8435</v>
+        <v>4574</v>
       </c>
       <c r="D3" t="n">
-        <v>16641</v>
+        <v>9372</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2312</v>
+        <v>637</v>
       </c>
       <c r="C4" t="n">
-        <v>7928</v>
+        <v>5435</v>
       </c>
       <c r="D4" t="n">
-        <v>8877</v>
+        <v>8220</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1322</v>
+        <v>644</v>
       </c>
       <c r="C5" t="n">
-        <v>5553</v>
+        <v>8736</v>
       </c>
       <c r="D5" t="n">
-        <v>3164</v>
+        <v>4055</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>845</v>
+        <v>369</v>
       </c>
       <c r="C6" t="n">
-        <v>3422</v>
+        <v>8455</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>309</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>2231</v>
+        <v>4659</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1151</v>
+        <v>1450</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
+        <v>223</v>
+      </c>
+      <c r="D10" t="n">
         <v>232</v>
-      </c>
-      <c r="D10" t="n">
-        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4371</v>
+        <v>509</v>
       </c>
       <c r="C2" t="n">
-        <v>7419</v>
+        <v>4682</v>
       </c>
       <c r="D2" t="n">
-        <v>22925</v>
+        <v>12295</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4104</v>
+        <v>316</v>
       </c>
       <c r="C3" t="n">
-        <v>5821</v>
+        <v>3707</v>
       </c>
       <c r="D3" t="n">
-        <v>16085</v>
+        <v>8496</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2991</v>
+        <v>492</v>
       </c>
       <c r="C4" t="n">
-        <v>8011</v>
+        <v>4933</v>
       </c>
       <c r="D4" t="n">
-        <v>9874</v>
+        <v>8147</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1550</v>
+        <v>594</v>
       </c>
       <c r="C5" t="n">
-        <v>6554</v>
+        <v>7128</v>
       </c>
       <c r="D5" t="n">
-        <v>3945</v>
+        <v>4531</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>962</v>
+        <v>435</v>
       </c>
       <c r="C6" t="n">
-        <v>4383</v>
+        <v>8494</v>
       </c>
       <c r="D6" t="n">
-        <v>1255</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>460</v>
+        <v>178</v>
       </c>
       <c r="C7" t="n">
-        <v>2743</v>
+        <v>6228</v>
       </c>
       <c r="D7" t="n">
-        <v>574</v>
+        <v>749</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>1617</v>
+        <v>2658</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>719</v>
+        <v>784</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2589</v>
+        <v>354</v>
       </c>
       <c r="C2" t="n">
-        <v>3455</v>
+        <v>2548</v>
       </c>
       <c r="D2" t="n">
-        <v>16026</v>
+        <v>8950</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4021</v>
+        <v>468</v>
       </c>
       <c r="C3" t="n">
-        <v>6180</v>
+        <v>4259</v>
       </c>
       <c r="D3" t="n">
-        <v>16436</v>
+        <v>9510</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3324</v>
+        <v>793</v>
       </c>
       <c r="C4" t="n">
-        <v>7898</v>
+        <v>7286</v>
       </c>
       <c r="D4" t="n">
-        <v>10622</v>
+        <v>8395</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1643</v>
+        <v>429</v>
       </c>
       <c r="C5" t="n">
-        <v>7821</v>
+        <v>11282</v>
       </c>
       <c r="D5" t="n">
-        <v>4168</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>816</v>
+        <v>164</v>
       </c>
       <c r="C6" t="n">
-        <v>5318</v>
+        <v>7934</v>
       </c>
       <c r="D6" t="n">
-        <v>1235</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>57</v>
       </c>
       <c r="C7" t="n">
-        <v>2921</v>
+        <v>2604</v>
       </c>
       <c r="D7" t="n">
-        <v>575</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>1195</v>
+        <v>768</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3345</v>
+        <v>172</v>
       </c>
       <c r="C2" t="n">
-        <v>5001</v>
+        <v>1306</v>
       </c>
       <c r="D2" t="n">
-        <v>14661</v>
+        <v>6883</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2938</v>
+        <v>358</v>
       </c>
       <c r="C3" t="n">
-        <v>4407</v>
+        <v>3051</v>
       </c>
       <c r="D3" t="n">
-        <v>15433</v>
+        <v>8765</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3148</v>
+        <v>540</v>
       </c>
       <c r="C4" t="n">
-        <v>6925</v>
+        <v>5490</v>
       </c>
       <c r="D4" t="n">
-        <v>11192</v>
+        <v>7979</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2051</v>
+        <v>407</v>
       </c>
       <c r="C5" t="n">
-        <v>7768</v>
+        <v>8316</v>
       </c>
       <c r="D5" t="n">
-        <v>4970</v>
+        <v>4217</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1036</v>
+        <v>154</v>
       </c>
       <c r="C6" t="n">
-        <v>6378</v>
+        <v>7717</v>
       </c>
       <c r="D6" t="n">
-        <v>1613</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>309</v>
+        <v>44</v>
       </c>
       <c r="C7" t="n">
-        <v>3940</v>
+        <v>3419</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1843</v>
+        <v>916</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>602</v>
+        <v>271</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>120</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2217</v>
+        <v>302</v>
       </c>
       <c r="C2" t="n">
-        <v>2596</v>
+        <v>3005</v>
       </c>
       <c r="D2" t="n">
-        <v>11937</v>
+        <v>8873</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2688</v>
+        <v>229</v>
       </c>
       <c r="C3" t="n">
-        <v>4254</v>
+        <v>1854</v>
       </c>
       <c r="D3" t="n">
-        <v>14500</v>
+        <v>7861</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2842</v>
+        <v>397</v>
       </c>
       <c r="C4" t="n">
-        <v>5898</v>
+        <v>4093</v>
       </c>
       <c r="D4" t="n">
-        <v>11529</v>
+        <v>7879</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2238</v>
+        <v>424</v>
       </c>
       <c r="C5" t="n">
-        <v>7597</v>
+        <v>6678</v>
       </c>
       <c r="D5" t="n">
-        <v>5631</v>
+        <v>4738</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1226</v>
+        <v>242</v>
       </c>
       <c r="C6" t="n">
-        <v>7074</v>
+        <v>8008</v>
       </c>
       <c r="D6" t="n">
-        <v>1915</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="C7" t="n">
-        <v>4806</v>
+        <v>5481</v>
       </c>
       <c r="D7" t="n">
-        <v>744</v>
+        <v>715</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>2363</v>
+        <v>2077</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>699</v>
+        <v>551</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3928</v>
+        <v>250</v>
       </c>
       <c r="C2" t="n">
-        <v>12992</v>
+        <v>10625</v>
       </c>
       <c r="D2" t="n">
-        <v>16030</v>
+        <v>9573</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2121</v>
+        <v>215</v>
       </c>
       <c r="C3" t="n">
-        <v>3221</v>
+        <v>2104</v>
       </c>
       <c r="D3" t="n">
-        <v>13264</v>
+        <v>7465</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2446</v>
+        <v>283</v>
       </c>
       <c r="C4" t="n">
-        <v>5080</v>
+        <v>2890</v>
       </c>
       <c r="D4" t="n">
-        <v>11606</v>
+        <v>7636</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2225</v>
+        <v>377</v>
       </c>
       <c r="C5" t="n">
-        <v>6753</v>
+        <v>5298</v>
       </c>
       <c r="D5" t="n">
-        <v>6252</v>
+        <v>5106</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1456</v>
+        <v>291</v>
       </c>
       <c r="C6" t="n">
-        <v>7215</v>
+        <v>7315</v>
       </c>
       <c r="D6" t="n">
-        <v>2354</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>510</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>5648</v>
+        <v>6617</v>
       </c>
       <c r="D7" t="n">
-        <v>866</v>
+        <v>909</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="C8" t="n">
-        <v>3247</v>
+        <v>3523</v>
       </c>
       <c r="D8" t="n">
-        <v>449</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>1243</v>
+        <v>1193</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>369</v>
+        <v>330</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5473</v>
+        <v>1678</v>
       </c>
       <c r="C2" t="n">
-        <v>8229</v>
+        <v>18229</v>
       </c>
       <c r="D2" t="n">
-        <v>6789</v>
+        <v>13735</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2807</v>
+        <v>187</v>
       </c>
       <c r="C2" t="n">
-        <v>7484</v>
+        <v>19843</v>
       </c>
       <c r="D2" t="n">
-        <v>11798</v>
+        <v>11873</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2944</v>
+        <v>189</v>
       </c>
       <c r="C3" t="n">
-        <v>5693</v>
+        <v>5065</v>
       </c>
       <c r="D3" t="n">
-        <v>14539</v>
+        <v>7245</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3286</v>
+        <v>223</v>
       </c>
       <c r="C4" t="n">
-        <v>7325</v>
+        <v>2475</v>
       </c>
       <c r="D4" t="n">
-        <v>11862</v>
+        <v>7377</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1407</v>
+        <v>312</v>
       </c>
       <c r="C5" t="n">
-        <v>10000</v>
+        <v>4096</v>
       </c>
       <c r="D5" t="n">
-        <v>5654</v>
+        <v>5266</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>471</v>
+        <v>300</v>
       </c>
       <c r="C6" t="n">
-        <v>6949</v>
+        <v>6395</v>
       </c>
       <c r="D6" t="n">
-        <v>1891</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>175</v>
       </c>
       <c r="C7" t="n">
-        <v>3182</v>
+        <v>6836</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>1218</v>
+        <v>4764</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>361</v>
+        <v>2083</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>639</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>197</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6392</v>
+        <v>3661</v>
       </c>
       <c r="C2" t="n">
-        <v>5077</v>
+        <v>9656</v>
       </c>
       <c r="D2" t="n">
-        <v>15117</v>
+        <v>16216</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2326</v>
+        <v>545</v>
       </c>
       <c r="C3" t="n">
-        <v>4147</v>
+        <v>7198</v>
       </c>
       <c r="D3" t="n">
-        <v>1779</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4597</v>
+        <v>2038</v>
       </c>
       <c r="C2" t="n">
-        <v>7874</v>
+        <v>8427</v>
       </c>
       <c r="D2" t="n">
-        <v>28508</v>
+        <v>20101</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3578</v>
+        <v>1795</v>
       </c>
       <c r="C3" t="n">
-        <v>4030</v>
+        <v>7508</v>
       </c>
       <c r="D3" t="n">
-        <v>3888</v>
+        <v>4716</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1044</v>
+        <v>280</v>
       </c>
       <c r="C4" t="n">
-        <v>2472</v>
+        <v>4471</v>
       </c>
       <c r="D4" t="n">
-        <v>1539</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5134</v>
+        <v>1365</v>
       </c>
       <c r="C2" t="n">
-        <v>7064</v>
+        <v>4573</v>
       </c>
       <c r="D2" t="n">
-        <v>21187</v>
+        <v>23977</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3356</v>
+        <v>1580</v>
       </c>
       <c r="C3" t="n">
-        <v>5302</v>
+        <v>6918</v>
       </c>
       <c r="D3" t="n">
-        <v>7547</v>
+        <v>6953</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1965</v>
+        <v>899</v>
       </c>
       <c r="C4" t="n">
-        <v>3303</v>
+        <v>6185</v>
       </c>
       <c r="D4" t="n">
-        <v>1943</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>480</v>
+        <v>167</v>
       </c>
       <c r="C5" t="n">
-        <v>1447</v>
+        <v>2659</v>
       </c>
       <c r="D5" t="n">
-        <v>1202</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>631</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5423</v>
+        <v>997</v>
       </c>
       <c r="C2" t="n">
-        <v>6369</v>
+        <v>10373</v>
       </c>
       <c r="D2" t="n">
-        <v>20281</v>
+        <v>27128</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3445</v>
+        <v>1221</v>
       </c>
       <c r="C3" t="n">
-        <v>5404</v>
+        <v>4911</v>
       </c>
       <c r="D3" t="n">
-        <v>9088</v>
+        <v>9176</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2264</v>
+        <v>1065</v>
       </c>
       <c r="C4" t="n">
-        <v>4308</v>
+        <v>6464</v>
       </c>
       <c r="D4" t="n">
-        <v>2906</v>
+        <v>3041</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1001</v>
+        <v>444</v>
       </c>
       <c r="C5" t="n">
-        <v>2365</v>
+        <v>4473</v>
       </c>
       <c r="D5" t="n">
-        <v>1281</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>274</v>
+        <v>127</v>
       </c>
       <c r="C6" t="n">
-        <v>882</v>
+        <v>1525</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>830</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5497</v>
+        <v>1170</v>
       </c>
       <c r="C2" t="n">
-        <v>7355</v>
+        <v>11024</v>
       </c>
       <c r="D2" t="n">
-        <v>23242</v>
+        <v>21699</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3201</v>
+        <v>928</v>
       </c>
       <c r="C3" t="n">
-        <v>4831</v>
+        <v>6685</v>
       </c>
       <c r="D3" t="n">
-        <v>9549</v>
+        <v>11258</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1760</v>
+        <v>986</v>
       </c>
       <c r="C4" t="n">
-        <v>4023</v>
+        <v>5509</v>
       </c>
       <c r="D4" t="n">
-        <v>3443</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>855</v>
+        <v>633</v>
       </c>
       <c r="C5" t="n">
-        <v>2447</v>
+        <v>5392</v>
       </c>
       <c r="D5" t="n">
-        <v>1223</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>299</v>
+        <v>245</v>
       </c>
       <c r="C6" t="n">
-        <v>1098</v>
+        <v>2952</v>
       </c>
       <c r="D6" t="n">
-        <v>764</v>
+        <v>883</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>389</v>
+        <v>882</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4927</v>
+        <v>1492</v>
       </c>
       <c r="C2" t="n">
-        <v>10017</v>
+        <v>15746</v>
       </c>
       <c r="D2" t="n">
-        <v>20244</v>
+        <v>20466</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3612</v>
+        <v>853</v>
       </c>
       <c r="C3" t="n">
-        <v>5422</v>
+        <v>7642</v>
       </c>
       <c r="D3" t="n">
-        <v>11146</v>
+        <v>11921</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2180</v>
+        <v>835</v>
       </c>
       <c r="C4" t="n">
-        <v>4389</v>
+        <v>5970</v>
       </c>
       <c r="D4" t="n">
-        <v>4536</v>
+        <v>5077</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1159</v>
+        <v>695</v>
       </c>
       <c r="C5" t="n">
-        <v>3334</v>
+        <v>5283</v>
       </c>
       <c r="D5" t="n">
-        <v>1633</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>538</v>
+        <v>374</v>
       </c>
       <c r="C6" t="n">
-        <v>1861</v>
+        <v>4046</v>
       </c>
       <c r="D6" t="n">
-        <v>833</v>
+        <v>963</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="C7" t="n">
-        <v>791</v>
+        <v>1806</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>314</v>
+        <v>557</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3601</v>
+        <v>1346</v>
       </c>
       <c r="C2" t="n">
-        <v>6001</v>
+        <v>9951</v>
       </c>
       <c r="D2" t="n">
-        <v>19480</v>
+        <v>16274</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3500</v>
+        <v>1285</v>
       </c>
       <c r="C3" t="n">
-        <v>6862</v>
+        <v>12102</v>
       </c>
       <c r="D3" t="n">
-        <v>11799</v>
+        <v>13004</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2473</v>
+        <v>642</v>
       </c>
       <c r="C4" t="n">
-        <v>4882</v>
+        <v>8682</v>
       </c>
       <c r="D4" t="n">
-        <v>5667</v>
+        <v>4693</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1469</v>
+        <v>345</v>
       </c>
       <c r="C5" t="n">
-        <v>3809</v>
+        <v>3965</v>
       </c>
       <c r="D5" t="n">
-        <v>2097</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>766</v>
+        <v>136</v>
       </c>
       <c r="C6" t="n">
-        <v>2631</v>
+        <v>1769</v>
       </c>
       <c r="D6" t="n">
-        <v>967</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>317</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>1356</v>
+        <v>545</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>556</v>
+        <v>279</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
